--- a/human_resources_forms/037_principal_on_site_restaurant_manager_application_form--human_resources_forms.xlsx
+++ b/human_resources_forms/037_principal_on_site_restaurant_manager_application_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Form Title</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Principal On Site Restaurant Manager Application Form</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,23 +542,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>contact_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Contact Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +570,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +593,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>category_label</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Contact Phone Number</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +616,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>description_label</t>
+          <t>current_work_place</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Current Work Place</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +639,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>employment_duration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Employment Duration</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,40 +657,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Job Title</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>category_label</t>
+          <t>availability</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +703,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>description_label</t>
+          <t>work_hours</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Work Hours</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +731,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>previous_work_experience</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Previous Work Experience</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +749,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>previous_restaurants_worked</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Previous Restaurants Worked</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>category_label</t>
+          <t>job_title_at_restaurant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Job Title at Restaurant</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +795,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>description_label</t>
+          <t>language_skills</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Language Skills</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +823,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>qualifications</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Qualifications</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,343 +864,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>category_label</t>
+          <t>certification</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Certifications</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>description_label</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>category_label</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>description_label</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>category_label</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>description_label</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>category_label</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>description_label</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1213,12 +895,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1241,34 +923,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>job_title_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>human_resources_forms</t>
+          <t>waiter/server</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Human Resources Forms</t>
+          <t>Waiter/Server</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>job_title_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>restaurant_manager_forms</t>
+          <t>kitchen_staff</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Restaurant Manager Forms</t>
+          <t>Kitchen Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>job_title_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>host/hostess</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Host/Hostess</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>job_title_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>bartender</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bartender</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>job_title_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>chef/cook</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chef/Cook</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>job_title_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>restaurant_manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Restaurant Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>job_title_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>previous_restaurants_worked_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>restaurant_a</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Restaurant A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>previous_restaurants_worked_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>restaurant_b</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Restaurant B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>previous_restaurants_worked_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>restaurant_c</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Restaurant C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>language_skills_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>language_skills_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>spanish</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>language_skills_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>french</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>language_skills_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>german</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>language_skills_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>certification_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>food_safety_certification</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Food Safety Certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>certification_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>service_certification</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Service Certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>certification_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
